--- a/inst/resources/quality_schema_data_quality_fsl_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_fsl_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB56B479-A392-4D26-AE42-C6D4D1141482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E8A736-309E-4938-BB58-7BAA80B7ADBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="quality_schema_fsl" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="101">
   <si>
     <t>check_name</t>
   </si>
@@ -305,6 +305,24 @@
   </si>
   <si>
     <t>FSL Cross-Variable Checks</t>
+  </si>
+  <si>
+    <t>plaus_flag_lcsi_coherence</t>
+  </si>
+  <si>
+    <t>plaus_flag_lcsi_na</t>
+  </si>
+  <si>
+    <t>% Flag Incoherent LCSI Responses</t>
+  </si>
+  <si>
+    <t>% Flag 4+ LCS Not Applicable</t>
+  </si>
+  <si>
+    <t>flag_lcsi_coherence</t>
+  </si>
+  <si>
+    <t>flag_lcsi_na</t>
   </si>
 </sst>
 </file>
@@ -682,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -1811,22 +1829,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
         <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -1837,16 +1855,16 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E46" t="s">
         <v>65</v>
@@ -1855,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" t="s">
         <v>47</v>
@@ -1863,16 +1881,16 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
         <v>65</v>
@@ -1881,7 +1899,7 @@
         <v>16</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H47" t="s">
         <v>47</v>
@@ -1889,80 +1907,80 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F49" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F50" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -1970,25 +1988,25 @@
         <v>94</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -1996,25 +2014,25 @@
         <v>94</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H52" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -2022,25 +2040,25 @@
         <v>94</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H53" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -2048,13 +2066,13 @@
         <v>94</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" t="s">
         <v>66</v>
@@ -2074,13 +2092,13 @@
         <v>94</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E55" t="s">
         <v>66</v>
@@ -2100,13 +2118,13 @@
         <v>94</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E56" t="s">
         <v>66</v>
@@ -2126,13 +2144,13 @@
         <v>94</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E57" t="s">
         <v>66</v>
@@ -2152,13 +2170,13 @@
         <v>94</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E58" t="s">
         <v>66</v>
@@ -2178,13 +2196,13 @@
         <v>94</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E59" t="s">
         <v>66</v>
@@ -2204,19 +2222,19 @@
         <v>94</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" t="s">
         <v>66</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2230,19 +2248,19 @@
         <v>94</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" t="s">
         <v>66</v>
       </c>
       <c r="F61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2256,13 +2274,13 @@
         <v>94</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" t="s">
         <v>66</v>
@@ -2282,13 +2300,13 @@
         <v>94</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E63" t="s">
         <v>66</v>
@@ -2308,19 +2326,19 @@
         <v>94</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E64" t="s">
         <v>66</v>
       </c>
       <c r="F64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G64">
         <v>4</v>
@@ -2334,19 +2352,19 @@
         <v>94</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" t="s">
         <v>66</v>
       </c>
       <c r="F65" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G65">
         <v>5</v>
@@ -2360,25 +2378,25 @@
         <v>94</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -2386,25 +2404,25 @@
         <v>94</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F67" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -2412,25 +2430,25 @@
         <v>94</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -2438,25 +2456,25 @@
         <v>94</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E69" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F69" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -2464,25 +2482,25 @@
         <v>94</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D70" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E70" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -2490,24 +2508,180 @@
         <v>94</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D71" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" t="s">
+        <v>66</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71">
+        <v>5</v>
+      </c>
+      <c r="H71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>94</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D72" t="s">
+        <v>60</v>
+      </c>
+      <c r="E72" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73" t="s">
+        <v>60</v>
+      </c>
+      <c r="E73" t="s">
+        <v>67</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D74" t="s">
+        <v>60</v>
+      </c>
+      <c r="E74" t="s">
+        <v>67</v>
+      </c>
+      <c r="F74" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74">
+        <v>3</v>
+      </c>
+      <c r="H74" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D75" t="s">
         <v>61</v>
       </c>
-      <c r="E71" t="s">
-        <v>65</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="E75" t="s">
+        <v>65</v>
+      </c>
+      <c r="F75" t="s">
+        <v>31</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76" t="s">
+        <v>65</v>
+      </c>
+      <c r="F76" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D77" t="s">
+        <v>61</v>
+      </c>
+      <c r="E77" t="s">
+        <v>65</v>
+      </c>
+      <c r="F77" t="s">
         <v>16</v>
       </c>
-      <c r="G71">
+      <c r="G77">
         <v>3</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H77" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2522,5 +2696,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>